--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CLASS BASQUET SANT ANTONI.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CLASS BASQUET SANT ANTONI.xlsx
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>22.9081</v>
+        <v>24.213</v>
       </c>
       <c r="E2" t="n">
-        <v>13.7697</v>
+        <v>12.1579</v>
       </c>
       <c r="F2" t="n">
-        <v>9.138500000000001</v>
+        <v>12.0552</v>
       </c>
       <c r="G2" t="n">
-        <v>5.321499999999999</v>
+        <v>6.2898</v>
       </c>
       <c r="H2" t="n">
-        <v>5.7018</v>
+        <v>6.161099999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3803000000000001</v>
+        <v>0.1286</v>
       </c>
       <c r="J2" t="n">
-        <v>6.9309</v>
+        <v>7.839399999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>5.982600000000001</v>
+        <v>6.766</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9485</v>
+        <v>1.0735</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.6094</v>
+        <v>-1.5497</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2808</v>
+        <v>-0.6049</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.3287</v>
+        <v>-0.9448</v>
       </c>
       <c r="P2" t="n">
-        <v>3.6873</v>
+        <v>3.0367</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.6629</v>
+        <v>-5.6688</v>
       </c>
       <c r="R2" t="n">
-        <v>6.3502</v>
+        <v>8.705500000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>10.2515</v>
+        <v>11.3416</v>
       </c>
       <c r="T2" t="n">
-        <v>6.3083</v>
+        <v>6.7608</v>
       </c>
       <c r="U2" t="n">
-        <v>3.9431</v>
+        <v>4.5811</v>
       </c>
       <c r="V2" t="n">
-        <v>3.648</v>
+        <v>3.5448</v>
       </c>
       <c r="W2" t="n">
-        <v>3.1936</v>
+        <v>3.2264</v>
       </c>
       <c r="X2" t="n">
-        <v>0.4544</v>
+        <v>0.3184</v>
       </c>
     </row>
     <row r="3">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>12.9832</v>
+        <v>15.0814</v>
       </c>
       <c r="E3" t="n">
-        <v>13.0951</v>
+        <v>10.8356</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1118999999999999</v>
+        <v>4.2458</v>
       </c>
       <c r="G3" t="n">
-        <v>18.2562</v>
+        <v>17.7151</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1714</v>
+        <v>3.2797</v>
       </c>
       <c r="I3" t="n">
-        <v>16.0847</v>
+        <v>14.4354</v>
       </c>
       <c r="J3" t="n">
-        <v>20.5874</v>
+        <v>18.761</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1493</v>
+        <v>3.7462</v>
       </c>
       <c r="L3" t="n">
-        <v>17.4382</v>
+        <v>15.0148</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.3313</v>
+        <v>-1.0459</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9778</v>
+        <v>-0.4663999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3534</v>
+        <v>-0.5793</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4098000000000001</v>
+        <v>0.6075000000000002</v>
       </c>
       <c r="Q3" t="n">
-        <v>-5.9405</v>
+        <v>-6.8835</v>
       </c>
       <c r="R3" t="n">
-        <v>5.5308</v>
+        <v>7.4908</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8671</v>
+        <v>0.5419</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3394</v>
+        <v>-0.5114000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4723999999999999</v>
+        <v>1.0533</v>
       </c>
       <c r="V3" t="n">
-        <v>-3.9962</v>
+        <v>-3.7829</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.2124</v>
+        <v>-0.5306</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.7839</v>
+        <v>-3.2522</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SOLARIN</t>
+          <t>G. GANTT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>11.9426</v>
+        <v>11.5019</v>
       </c>
       <c r="E4" t="n">
-        <v>10.6805</v>
+        <v>10.414</v>
       </c>
       <c r="F4" t="n">
-        <v>1.262</v>
+        <v>1.0877</v>
       </c>
       <c r="G4" t="n">
-        <v>7.7072</v>
+        <v>14.6003</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0543</v>
+        <v>-0.3283000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>5.652800000000001</v>
+        <v>14.9283</v>
       </c>
       <c r="J4" t="n">
-        <v>10.6875</v>
+        <v>17.7518</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7288</v>
+        <v>0.966</v>
       </c>
       <c r="L4" t="n">
-        <v>6.9586</v>
+        <v>16.7858</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.9803</v>
+        <v>-3.1517</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6744</v>
+        <v>-1.2943</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3057</v>
+        <v>-1.8574</v>
       </c>
       <c r="P4" t="n">
-        <v>4.0968</v>
+        <v>4.0491</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0242</v>
+        <v>-5.4663</v>
       </c>
       <c r="R4" t="n">
-        <v>5.1211</v>
+        <v>9.5153</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6673</v>
+        <v>-4.2781</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2909999999999999</v>
+        <v>-2.7177</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3762</v>
+        <v>-1.5604</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.5289</v>
+        <v>-2.8694</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7262</v>
+        <v>0.846</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.255</v>
+        <v>-3.7154</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. DE LA RUA DE AGUSTIN</t>
+          <t>J. SOLARIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>10.204</v>
+        <v>10.9389</v>
       </c>
       <c r="E5" t="n">
-        <v>7.821099999999999</v>
+        <v>8.6328</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3829</v>
+        <v>2.306</v>
       </c>
       <c r="G5" t="n">
-        <v>16.0167</v>
+        <v>6.6167</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2531</v>
+        <v>1.5618</v>
       </c>
       <c r="I5" t="n">
-        <v>13.7637</v>
+        <v>5.0549</v>
       </c>
       <c r="J5" t="n">
-        <v>17.862</v>
+        <v>8.9969</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3954</v>
+        <v>3.2741</v>
       </c>
       <c r="L5" t="n">
-        <v>15.4664</v>
+        <v>5.723</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8451</v>
+        <v>-2.3801</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1422000000000001</v>
+        <v>-1.7122</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7027</v>
+        <v>-0.6679999999999998</v>
       </c>
       <c r="P5" t="n">
-        <v>-5.1211</v>
+        <v>5.061500000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>-13.7248</v>
+        <v>-1.0123</v>
       </c>
       <c r="R5" t="n">
-        <v>8.6036</v>
+        <v>6.0737</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5735999999999999</v>
+        <v>0.9141000000000004</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6900999999999999</v>
+        <v>-0.1046</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1165999999999999</v>
+        <v>1.0188</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1181000000000001</v>
+        <v>-1.6533</v>
       </c>
       <c r="W5" t="n">
-        <v>4.3742</v>
+        <v>0.7528</v>
       </c>
       <c r="X5" t="n">
-        <v>-4.4923</v>
+        <v>-2.4062</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. GANTT</t>
+          <t>D. DE LA RUA DE AGUSTIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>7.4716</v>
+        <v>8.2598</v>
       </c>
       <c r="E6" t="n">
-        <v>8.2309</v>
+        <v>8.0665</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7593000000000001</v>
+        <v>0.1932</v>
       </c>
       <c r="G6" t="n">
-        <v>9.858499999999999</v>
+        <v>17.4676</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3855</v>
+        <v>6.1437</v>
       </c>
       <c r="I6" t="n">
-        <v>9.472999999999999</v>
+        <v>11.3241</v>
       </c>
       <c r="J6" t="n">
-        <v>13.1298</v>
+        <v>21.0118</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2801</v>
+        <v>7.397500000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>11.8498</v>
+        <v>13.6145</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.2713</v>
+        <v>-3.5442</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8944</v>
+        <v>-1.254</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.3767</v>
+        <v>-2.2905</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0727</v>
+        <v>-5.8712</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.4823</v>
+        <v>-16.6011</v>
       </c>
       <c r="R6" t="n">
-        <v>6.5551</v>
+        <v>10.73</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.9804</v>
+        <v>-1.4325</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.6584</v>
+        <v>-1.3561</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.3219</v>
+        <v>-0.07639999999999991</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.4793</v>
+        <v>-1.9043</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2421</v>
+        <v>5.011699999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.7214</v>
+        <v>-6.916</v>
       </c>
     </row>
     <row r="7">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>6.019100000000001</v>
+        <v>7.469900000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>10.0287</v>
+        <v>9.196400000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.0098</v>
+        <v>-1.7267</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5229</v>
+        <v>0.6615000000000002</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1502</v>
+        <v>0.3884000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3728000000000002</v>
+        <v>0.2730999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>4.3433</v>
+        <v>4.1859</v>
       </c>
       <c r="K7" t="n">
-        <v>2.406899999999999</v>
+        <v>2.1582</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9363</v>
+        <v>2.0274</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.8202</v>
+        <v>-3.5243</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2568</v>
+        <v>-1.7699</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5634</v>
+        <v>-1.7544</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4339</v>
+        <v>0.2025000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.3017</v>
+        <v>-7.288399999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>5.7356</v>
+        <v>7.4909</v>
       </c>
       <c r="S7" t="n">
-        <v>5.2994</v>
+        <v>8.4169</v>
       </c>
       <c r="T7" t="n">
-        <v>5.235300000000001</v>
+        <v>7.4735</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06429999999999994</v>
+        <v>0.9433</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.2372</v>
+        <v>-1.8111</v>
       </c>
       <c r="W7" t="n">
-        <v>4.7523</v>
+        <v>4.8251</v>
       </c>
       <c r="X7" t="n">
-        <v>-6.9893</v>
+        <v>-6.6364</v>
       </c>
     </row>
     <row r="8">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>4.4838</v>
+        <v>6.5153</v>
       </c>
       <c r="E8" t="n">
-        <v>4.1366</v>
+        <v>4.1459</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3472000000000008</v>
+        <v>2.3692</v>
       </c>
       <c r="G8" t="n">
-        <v>10.0176</v>
+        <v>12.7628</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2706</v>
+        <v>3.9461</v>
       </c>
       <c r="I8" t="n">
-        <v>7.7469</v>
+        <v>8.816599999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>11.3415</v>
+        <v>14.1205</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1691</v>
+        <v>6.9391</v>
       </c>
       <c r="L8" t="n">
-        <v>7.1724</v>
+        <v>7.181399999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3238</v>
+        <v>-1.3576</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8983</v>
+        <v>-2.9928</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5745</v>
+        <v>1.6353</v>
       </c>
       <c r="P8" t="n">
-        <v>-4.3019</v>
+        <v>-6.0735</v>
       </c>
       <c r="Q8" t="n">
-        <v>-12.2909</v>
+        <v>-17.2084</v>
       </c>
       <c r="R8" t="n">
-        <v>7.989</v>
+        <v>11.1349</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0077</v>
+        <v>-1.6281</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.4369</v>
+        <v>-1.6641</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4291999999999999</v>
+        <v>0.03589999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2242000000000002</v>
+        <v>1.454</v>
       </c>
       <c r="W8" t="n">
-        <v>6.523</v>
+        <v>8.8978</v>
       </c>
       <c r="X8" t="n">
-        <v>-6.747300000000001</v>
+        <v>-7.4437</v>
       </c>
     </row>
     <row r="9">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.05790000000000006</v>
+        <v>3.5524</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6811000000000007</v>
+        <v>3.7196</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7388000000000001</v>
+        <v>-0.1672000000000002</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.03690000000000015</v>
+        <v>0.9085999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4548999999999999</v>
+        <v>0.9690999999999996</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4181000000000001</v>
+        <v>-0.06039999999999979</v>
       </c>
       <c r="J9" t="n">
-        <v>1.914400000000001</v>
+        <v>3.5621</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1886000000000003</v>
+        <v>2.4219</v>
       </c>
       <c r="L9" t="n">
-        <v>1.7258</v>
+        <v>1.1405</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9513</v>
+        <v>-2.6534</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6435</v>
+        <v>-1.4528</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3077</v>
+        <v>-1.2008</v>
       </c>
       <c r="P9" t="n">
-        <v>2.0485</v>
+        <v>2.4294</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.9163</v>
+        <v>-6.8834</v>
       </c>
       <c r="R9" t="n">
-        <v>6.9647</v>
+        <v>9.312899999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>4.8902</v>
+        <v>7.8187</v>
       </c>
       <c r="T9" t="n">
-        <v>2.9567</v>
+        <v>5.097700000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>1.9334</v>
+        <v>2.7209</v>
       </c>
       <c r="V9" t="n">
-        <v>-6.9597</v>
+        <v>-7.6043</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7262</v>
+        <v>1.943</v>
       </c>
       <c r="X9" t="n">
-        <v>-7.6859</v>
+        <v>-9.5473</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. TVRDIC</t>
+          <t>J. RODRIGUEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2771</v>
+        <v>-2.8917</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0937</v>
+        <v>-3.1817</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1833999999999999</v>
+        <v>0.2900999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.8232</v>
+        <v>-1.9807</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8787</v>
+        <v>-0.6717000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.9447</v>
+        <v>-1.309</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.8302</v>
+        <v>-1.8164</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.7697</v>
+        <v>0.1172</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.06050000000000022</v>
+        <v>-1.9336</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9931000000000001</v>
+        <v>-0.1643000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>0.891</v>
+        <v>-0.7888999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.8841</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4338</v>
+        <v>1.4172</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0242</v>
+        <v>-0.4049</v>
       </c>
       <c r="R10" t="n">
-        <v>2.458</v>
+        <v>1.8221</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8877999999999999</v>
+        <v>-1.1379</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.662</v>
+        <v>-0.9604999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.226</v>
+        <v>-0.1774</v>
       </c>
       <c r="V10" t="n">
+        <v>-1.1902</v>
+      </c>
+      <c r="W10" t="n">
         <v>0</v>
       </c>
-      <c r="W10" t="n">
-        <v>1.4227</v>
-      </c>
       <c r="X10" t="n">
-        <v>-1.4227</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ JIMENEZ</t>
+          <t>L. TVRDIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5151</v>
+        <v>-4.3995</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1783</v>
+        <v>-3.8236</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3368000000000001</v>
+        <v>-0.5759000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.3738</v>
+        <v>-4.7713</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2544</v>
+        <v>-1.878</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.1193</v>
+        <v>-2.8934</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.8516</v>
+        <v>-3.4285</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2226</v>
+        <v>-2.7112</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.629</v>
+        <v>-0.7174000000000003</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5222000000000001</v>
+        <v>-1.3429</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0318</v>
+        <v>0.8331</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5096999999999999</v>
+        <v>-2.176</v>
       </c>
       <c r="P11" t="n">
-        <v>1.2291</v>
+        <v>1.4173</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.4097</v>
+        <v>-1.0123</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6388</v>
+        <v>2.4296</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1898</v>
+        <v>-1.0452</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.917</v>
+        <v>-0.8239</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2728</v>
+        <v>-0.2213</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.1806</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.4411</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1806</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="12">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.6322</v>
+        <v>-12.0916</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.9268</v>
+        <v>-11.118</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7053000000000003</v>
+        <v>-0.9738000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-9.381</v>
+        <v>-11.3341</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.5009</v>
+        <v>-3.6741</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.880100000000001</v>
+        <v>-7.6599</v>
       </c>
       <c r="J12" t="n">
-        <v>-6.0436</v>
+        <v>-7.175800000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4922</v>
+        <v>-1.032</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.5515</v>
+        <v>-6.143800000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.3374</v>
+        <v>-4.1583</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.0088</v>
+        <v>-2.6422</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3286</v>
+        <v>-1.5161</v>
       </c>
       <c r="P12" t="n">
-        <v>1.0241</v>
+        <v>1.8222</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4823</v>
+        <v>-3.4418</v>
       </c>
       <c r="R12" t="n">
-        <v>4.506600000000001</v>
+        <v>5.2638</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4340999999999999</v>
+        <v>0.1449000000000003</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5367</v>
+        <v>-0.6582999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9708999999999999</v>
+        <v>0.8031</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.7094</v>
+        <v>-2.7246</v>
       </c>
       <c r="W12" t="n">
-        <v>0.136</v>
+        <v>0.1576</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.8454</v>
+        <v>-2.8822</v>
       </c>
     </row>
     <row r="13">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>57.53009999999999</v>
+        <v>68.1498</v>
       </c>
       <c r="E13" t="n">
-        <v>51.24490000000001</v>
+        <v>49.0454</v>
       </c>
       <c r="F13" t="n">
-        <v>6.2853</v>
+        <v>19.1036</v>
       </c>
       <c r="G13" t="n">
-        <v>52.0857</v>
+        <v>58.93630000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>9.898</v>
+        <v>15.8978</v>
       </c>
       <c r="I13" t="n">
-        <v>42.1876</v>
+        <v>43.03830000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>75.0714</v>
+        <v>83.8087</v>
       </c>
       <c r="K13" t="n">
-        <v>19.8163</v>
+        <v>30.043</v>
       </c>
       <c r="L13" t="n">
-        <v>55.25500000000001</v>
+        <v>53.7661</v>
       </c>
       <c r="M13" t="n">
-        <v>-22.9854</v>
+        <v>-24.8724</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.9178</v>
+        <v>-14.1453</v>
       </c>
       <c r="O13" t="n">
-        <v>-13.0668</v>
+        <v>-10.7275</v>
       </c>
       <c r="P13" t="n">
-        <v>8.1934</v>
+        <v>8.098700000000003</v>
       </c>
       <c r="Q13" t="n">
-        <v>-53.25980000000001</v>
+        <v>-71.87119999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>61.4535</v>
+        <v>79.96950000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>15.0361</v>
+        <v>19.6563</v>
       </c>
       <c r="T13" t="n">
-        <v>7.550800000000001</v>
+        <v>10.5354</v>
       </c>
       <c r="U13" t="n">
-        <v>7.4854</v>
+        <v>9.120900000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-17.7856</v>
+        <v>-18.5413</v>
       </c>
       <c r="W13" t="n">
-        <v>21.8839</v>
+        <v>26.57089999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-39.6694</v>
+        <v>-45.11229999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CLASS BASQUET SANT ANTONI.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CLASS BASQUET SANT ANTONI.xlsx
@@ -565,13 +565,13 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>24.213</v>
+        <v>18.3535</v>
       </c>
       <c r="E2" t="n">
-        <v>12.1579</v>
+        <v>7.687</v>
       </c>
       <c r="F2" t="n">
-        <v>12.0552</v>
+        <v>10.6664</v>
       </c>
       <c r="G2" t="n">
         <v>6.2898</v>
@@ -610,13 +610,13 @@
         <v>8.705500000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>11.3416</v>
+        <v>5.4822</v>
       </c>
       <c r="T2" t="n">
-        <v>6.7608</v>
+        <v>2.2898</v>
       </c>
       <c r="U2" t="n">
-        <v>4.5811</v>
+        <v>3.1923</v>
       </c>
       <c r="V2" t="n">
         <v>3.5448</v>
@@ -643,13 +643,13 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>15.0814</v>
+        <v>16.3518</v>
       </c>
       <c r="E3" t="n">
-        <v>10.8356</v>
+        <v>11.6505</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2458</v>
+        <v>4.701099999999999</v>
       </c>
       <c r="G3" t="n">
         <v>17.7151</v>
@@ -688,13 +688,13 @@
         <v>7.4908</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5419</v>
+        <v>1.8123</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5114000000000001</v>
+        <v>0.3036</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0533</v>
+        <v>1.5087</v>
       </c>
       <c r="V3" t="n">
         <v>-3.7829</v>
@@ -721,13 +721,13 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>11.5019</v>
+        <v>15.8866</v>
       </c>
       <c r="E4" t="n">
-        <v>10.414</v>
+        <v>13.0181</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0877</v>
+        <v>2.8685</v>
       </c>
       <c r="G4" t="n">
         <v>14.6003</v>
@@ -766,13 +766,13 @@
         <v>9.5153</v>
       </c>
       <c r="S4" t="n">
-        <v>-4.2781</v>
+        <v>0.1069</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.7177</v>
+        <v>-0.1137000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.5604</v>
+        <v>0.2204</v>
       </c>
       <c r="V4" t="n">
         <v>-2.8694</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. SOLARIN</t>
+          <t>D. DE LA RUA DE AGUSTIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>10.9389</v>
+        <v>12.2885</v>
       </c>
       <c r="E5" t="n">
-        <v>8.6328</v>
+        <v>11.0462</v>
       </c>
       <c r="F5" t="n">
-        <v>2.306</v>
+        <v>1.2424</v>
       </c>
       <c r="G5" t="n">
-        <v>6.6167</v>
+        <v>17.4676</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5618</v>
+        <v>6.1437</v>
       </c>
       <c r="I5" t="n">
-        <v>5.0549</v>
+        <v>11.3241</v>
       </c>
       <c r="J5" t="n">
-        <v>8.9969</v>
+        <v>21.0118</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2741</v>
+        <v>7.397500000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>5.723</v>
+        <v>13.6145</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3801</v>
+        <v>-3.5442</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7122</v>
+        <v>-1.254</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6679999999999998</v>
+        <v>-2.2905</v>
       </c>
       <c r="P5" t="n">
-        <v>5.061500000000001</v>
+        <v>-5.8712</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0123</v>
+        <v>-16.6011</v>
       </c>
       <c r="R5" t="n">
-        <v>6.0737</v>
+        <v>10.73</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9141000000000004</v>
+        <v>2.5963</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1046</v>
+        <v>1.6234</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0188</v>
+        <v>0.9728</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.6533</v>
+        <v>-1.9043</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7528</v>
+        <v>5.011699999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.4062</v>
+        <v>-6.916</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. DE LA RUA DE AGUSTIN</t>
+          <t>J. SOLARIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>8.2598</v>
+        <v>10.8649</v>
       </c>
       <c r="E6" t="n">
-        <v>8.0665</v>
+        <v>8.8009</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1932</v>
+        <v>2.0641</v>
       </c>
       <c r="G6" t="n">
-        <v>17.4676</v>
+        <v>6.6167</v>
       </c>
       <c r="H6" t="n">
-        <v>6.1437</v>
+        <v>1.5618</v>
       </c>
       <c r="I6" t="n">
-        <v>11.3241</v>
+        <v>5.0549</v>
       </c>
       <c r="J6" t="n">
-        <v>21.0118</v>
+        <v>8.9969</v>
       </c>
       <c r="K6" t="n">
-        <v>7.397500000000001</v>
+        <v>3.2741</v>
       </c>
       <c r="L6" t="n">
-        <v>13.6145</v>
+        <v>5.723</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.5442</v>
+        <v>-2.3801</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.254</v>
+        <v>-1.7122</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.2905</v>
+        <v>-0.6679999999999998</v>
       </c>
       <c r="P6" t="n">
-        <v>-5.8712</v>
+        <v>5.061500000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-16.6011</v>
+        <v>-1.0123</v>
       </c>
       <c r="R6" t="n">
-        <v>10.73</v>
+        <v>6.0737</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4325</v>
+        <v>0.8402000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.3561</v>
+        <v>0.06320000000000002</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.07639999999999991</v>
+        <v>0.777</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.9043</v>
+        <v>-1.6533</v>
       </c>
       <c r="W6" t="n">
-        <v>5.011699999999999</v>
+        <v>0.7528</v>
       </c>
       <c r="X6" t="n">
-        <v>-6.916</v>
+        <v>-2.4062</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. STOILOV</t>
+          <t>K. JOHNSON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>7.469900000000001</v>
+        <v>10.6186</v>
       </c>
       <c r="E7" t="n">
-        <v>9.196400000000001</v>
+        <v>7.6843</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7267</v>
+        <v>2.9344</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6615000000000002</v>
+        <v>12.7628</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3884000000000001</v>
+        <v>3.9461</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2730999999999999</v>
+        <v>8.816599999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>4.1859</v>
+        <v>14.1205</v>
       </c>
       <c r="K7" t="n">
-        <v>2.1582</v>
+        <v>6.9391</v>
       </c>
       <c r="L7" t="n">
-        <v>2.0274</v>
+        <v>7.181399999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.5243</v>
+        <v>-1.3576</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7699</v>
+        <v>-2.9928</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7544</v>
+        <v>1.6353</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2025000000000001</v>
+        <v>-6.0735</v>
       </c>
       <c r="Q7" t="n">
-        <v>-7.288399999999999</v>
+        <v>-17.2084</v>
       </c>
       <c r="R7" t="n">
-        <v>7.4909</v>
+        <v>11.1349</v>
       </c>
       <c r="S7" t="n">
-        <v>8.4169</v>
+        <v>2.4753</v>
       </c>
       <c r="T7" t="n">
-        <v>7.4735</v>
+        <v>1.8744</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9433</v>
+        <v>0.6007999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.8111</v>
+        <v>1.454</v>
       </c>
       <c r="W7" t="n">
-        <v>4.8251</v>
+        <v>8.8978</v>
       </c>
       <c r="X7" t="n">
-        <v>-6.6364</v>
+        <v>-7.4437</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. JOHNSON</t>
+          <t>E. STOILOV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>6.5153</v>
+        <v>2.5576</v>
       </c>
       <c r="E8" t="n">
-        <v>4.1459</v>
+        <v>4.7568</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3692</v>
+        <v>-2.199000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>12.7628</v>
+        <v>0.6615000000000002</v>
       </c>
       <c r="H8" t="n">
-        <v>3.9461</v>
+        <v>0.3884000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>8.816599999999999</v>
+        <v>0.2730999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>14.1205</v>
+        <v>4.1859</v>
       </c>
       <c r="K8" t="n">
-        <v>6.9391</v>
+        <v>2.1582</v>
       </c>
       <c r="L8" t="n">
-        <v>7.181399999999999</v>
+        <v>2.0274</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3576</v>
+        <v>-3.5243</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.9928</v>
+        <v>-1.7699</v>
       </c>
       <c r="O8" t="n">
-        <v>1.6353</v>
+        <v>-1.7544</v>
       </c>
       <c r="P8" t="n">
-        <v>-6.0735</v>
+        <v>0.2025000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-17.2084</v>
+        <v>-7.288399999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>11.1349</v>
+        <v>7.4909</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6281</v>
+        <v>3.5048</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.6641</v>
+        <v>3.0338</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03589999999999999</v>
+        <v>0.4709</v>
       </c>
       <c r="V8" t="n">
-        <v>1.454</v>
+        <v>-1.8111</v>
       </c>
       <c r="W8" t="n">
-        <v>8.8978</v>
+        <v>4.8251</v>
       </c>
       <c r="X8" t="n">
-        <v>-7.4437</v>
+        <v>-6.6364</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>3.5524</v>
+        <v>1.0832</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7196</v>
+        <v>2.091699999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1672000000000002</v>
+        <v>-1.0085</v>
       </c>
       <c r="G9" t="n">
         <v>0.9085999999999999</v>
@@ -1156,13 +1156,13 @@
         <v>9.312899999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>7.8187</v>
+        <v>5.3494</v>
       </c>
       <c r="T9" t="n">
-        <v>5.097700000000001</v>
+        <v>3.4697</v>
       </c>
       <c r="U9" t="n">
-        <v>2.7209</v>
+        <v>1.8796</v>
       </c>
       <c r="V9" t="n">
         <v>-7.6043</v>
@@ -1189,13 +1189,13 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8917</v>
+        <v>-1.5694</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1817</v>
+        <v>-2.2629</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2900999999999999</v>
+        <v>0.6935000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9807</v>
@@ -1234,13 +1234,13 @@
         <v>1.8221</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1379</v>
+        <v>0.1843</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9604999999999999</v>
+        <v>-0.0417</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1774</v>
+        <v>0.226</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1902</v>
@@ -1267,13 +1267,13 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3995</v>
+        <v>-3.24</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8236</v>
+        <v>-3.2404</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5759000000000001</v>
+        <v>0.0004000000000000115</v>
       </c>
       <c r="G11" t="n">
         <v>-4.7713</v>
@@ -1312,13 +1312,13 @@
         <v>2.4296</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0452</v>
+        <v>0.1141</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8239</v>
+        <v>-0.2409</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2213</v>
+        <v>0.355</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.0916</v>
+        <v>-10.0881</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.118</v>
+        <v>-9.3047</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9738000000000001</v>
+        <v>-0.7831999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-11.3341</v>
@@ -1390,13 +1390,13 @@
         <v>5.2638</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1449000000000003</v>
+        <v>2.1486</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6582999999999999</v>
+        <v>1.1551</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8031</v>
+        <v>0.9934999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-2.7246</v>
@@ -1423,13 +1423,13 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>68.1498</v>
+        <v>73.10719999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>49.0454</v>
+        <v>51.92749999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>19.1036</v>
+        <v>21.1801</v>
       </c>
       <c r="G13" t="n">
         <v>58.93630000000001</v>
@@ -1438,7 +1438,7 @@
         <v>15.8978</v>
       </c>
       <c r="I13" t="n">
-        <v>43.03830000000001</v>
+        <v>43.0383</v>
       </c>
       <c r="J13" t="n">
         <v>83.8087</v>
@@ -1459,7 +1459,7 @@
         <v>-10.7275</v>
       </c>
       <c r="P13" t="n">
-        <v>8.098700000000003</v>
+        <v>8.098700000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-71.87119999999999</v>
@@ -1468,19 +1468,19 @@
         <v>79.96950000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>19.6563</v>
+        <v>24.6144</v>
       </c>
       <c r="T13" t="n">
-        <v>10.5354</v>
+        <v>13.4167</v>
       </c>
       <c r="U13" t="n">
-        <v>9.120900000000001</v>
+        <v>11.197</v>
       </c>
       <c r="V13" t="n">
         <v>-18.5413</v>
       </c>
       <c r="W13" t="n">
-        <v>26.57089999999999</v>
+        <v>26.5709</v>
       </c>
       <c r="X13" t="n">
         <v>-45.11229999999999</v>
